--- a/public/bulk-order-template.xlsx
+++ b/public/bulk-order-template.xlsx
@@ -399,31 +399,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:W4"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="13.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="13.83203125" customWidth="1"/>
-    <col min="22" max="22" width="14.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -718,11 +693,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="110.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -742,7 +713,7 @@
         <v>Multiple products</v>
       </c>
       <c r="B4" t="str">
-        <v>Repeat the same Order number on several rows. Customer, payment and package columns are read from the first row of that order.</v>
+        <v>Repeat the same Order number on several rows (one row per product, maximum 5 products per order). Customer, payment and package columns are read from the first row of that order.</v>
       </c>
     </row>
     <row r="5">
@@ -787,15 +758,23 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>Product limit</v>
+      </c>
+      <c r="B10" t="str">
+        <v>An order can contain at most 5 products. A sheet with more than 5 rows for one order number is rejected for that order.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Note</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B11" t="str">
         <v>Delete the sample rows before uploading your own orders. Keep the header row unchanged.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/bulk-order-template.xlsx
+++ b/public/bulk-order-template.xlsx
@@ -118,74 +118,67 @@
     <comment ref="O1" authorId="0">
       <text>
         <r>
-          <t>Optional. Name of the pickup warehouse exactly as in Settings &gt; Warehouse. Leave blank to use the warehouse chosen on the upload page.</t>
+          <t>Optional. The ID of the pickup warehouse as shown in Settings &gt; Warehouse (for example WH000004). Leave blank to use the warehouse chosen on the upload page.</t>
         </r>
       </text>
     </comment>
     <comment ref="P1" authorId="0">
       <text>
         <r>
-          <t>Optional. Address (or pincode) of the pickup warehouse. Use it instead of the name, or with it. Leave blank to use the warehouse chosen on the upload page.</t>
+          <t>Optional. A SKU saved in your catalog auto-fills product name, HSN, price and weight.</t>
         </r>
       </text>
     </comment>
     <comment ref="Q1" authorId="0">
       <text>
         <r>
-          <t>Optional. A SKU saved in your catalog auto-fills product name, HSN, price and weight.</t>
+          <t>MANDATORY. Required unless the SKU is saved in your catalog.</t>
         </r>
       </text>
     </comment>
     <comment ref="R1" authorId="0">
       <text>
         <r>
-          <t>MANDATORY. Required unless the SKU is saved in your catalog.</t>
+          <t>Optional. Optional, 4 to 8 digits.</t>
         </r>
       </text>
     </comment>
     <comment ref="S1" authorId="0">
       <text>
         <r>
-          <t>Optional. Optional, 4 to 8 digits.</t>
+          <t>MANDATORY. Whole number.</t>
         </r>
       </text>
     </comment>
     <comment ref="T1" authorId="0">
       <text>
         <r>
-          <t>MANDATORY. Whole number.</t>
+          <t>MANDATORY. Price of one unit in rupees.</t>
         </r>
       </text>
     </comment>
     <comment ref="U1" authorId="0">
       <text>
         <r>
-          <t>MANDATORY. Price of one unit in rupees.</t>
+          <t>MANDATORY. Weight of one unit in grams.</t>
         </r>
       </text>
     </comment>
     <comment ref="V1" authorId="0">
       <text>
         <r>
-          <t>MANDATORY. Weight of one unit in grams.</t>
+          <t>MANDATORY. Parcel length in cm.</t>
         </r>
       </text>
     </comment>
     <comment ref="W1" authorId="0">
       <text>
         <r>
-          <t>MANDATORY. Parcel length in cm.</t>
+          <t>MANDATORY. Parcel breadth in cm.</t>
         </r>
       </text>
     </comment>
     <comment ref="X1" authorId="0">
-      <text>
-        <r>
-          <t>MANDATORY. Parcel breadth in cm.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0">
       <text>
         <r>
           <t>MANDATORY. Parcel height in cm.</t>
@@ -197,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>Order number *</t>
   </si>
@@ -241,10 +234,7 @@
     <t>State</t>
   </si>
   <si>
-    <t>Pickup warehouse</t>
-  </si>
-  <si>
-    <t>Pickup warehouse address</t>
+    <t>Warehouse ID</t>
   </si>
   <si>
     <t>SKU</t>
@@ -310,10 +300,7 @@
     <t>Karnataka</t>
   </si>
   <si>
-    <t>Main warehouse</t>
-  </si>
-  <si>
-    <t>14 Industrial Area, Mumbai 400001</t>
+    <t>WH000001</t>
   </si>
   <si>
     <t>DEMO-KIT-01</t>
@@ -411,13 +398,13 @@
     <t>Choose Prepaid or COD from the list. Prepaid is listed first.</t>
   </si>
   <si>
-    <t>Optional. Type the warehouse name exactly as in Settings &gt; Warehouse, or its address / pincode. Blank = the warehouse selected on the upload page.</t>
+    <t>Optional. The warehouse ID from Settings &gt; Warehouse (for example WH000004). Blank = the warehouse selected on the upload page.</t>
   </si>
   <si>
     <t>City / State</t>
   </si>
   <si>
-    <t>Optional. Filled automatically from the pincode when left blank.</t>
+    <t>Optional. Filled automatically from the pincode (India Post directory) when left blank. Only fill them in if the upload says it could not find the pincode.</t>
   </si>
   <si>
     <t>Use a SKU saved in your catalog to auto-fill product name, HSN, price and weight.</t>
@@ -474,10 +461,7 @@
     <t>Optional. Optional: filled automatically from the pincode when blank.</t>
   </si>
   <si>
-    <t>Optional. Name of the pickup warehouse exactly as in Settings &gt; Warehouse. Leave blank to use the warehouse chosen on the upload page.</t>
-  </si>
-  <si>
-    <t>Optional. Address (or pincode) of the pickup warehouse. Use it instead of the name, or with it. Leave blank to use the warehouse chosen on the upload page.</t>
+    <t>Optional. The ID of the pickup warehouse as shown in Settings &gt; Warehouse (for example WH000004). Leave blank to use the warehouse chosen on the upload page.</t>
   </si>
   <si>
     <t>Optional. A SKU saved in your catalog auto-fills product name, HSN, price and weight.</t>
@@ -953,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y201"/>
+  <dimension ref="A1:X201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="17" customWidth="1"/>
@@ -969,19 +953,18 @@
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="30" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="22" customWidth="1"/>
-    <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="22" width="15" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="17" customWidth="1"/>
-    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="21" width="15" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="17" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1030,13 +1013,13 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
@@ -1054,242 +1037,230 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4">
+        <v>1</v>
+      </c>
+      <c r="T2" s="4">
+        <v>1299.5</v>
+      </c>
+      <c r="U2" s="4">
+        <v>500</v>
+      </c>
+      <c r="V2" s="4">
+        <v>20</v>
+      </c>
+      <c r="W2" s="4">
+        <v>15</v>
+      </c>
+      <c r="X2" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="4">
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" s="4">
+        <v>2</v>
+      </c>
+      <c r="T3" s="4">
+        <v>799</v>
+      </c>
+      <c r="U3" s="4">
+        <v>350</v>
+      </c>
+      <c r="V3" s="4">
+        <v>30</v>
+      </c>
+      <c r="W3" s="4">
+        <v>25</v>
+      </c>
+      <c r="X3" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="S4" s="4">
         <v>1</v>
       </c>
-      <c r="U2" s="4">
-        <v>1299.5</v>
-      </c>
-      <c r="V2" s="4">
-        <v>500</v>
-      </c>
-      <c r="W2" s="4">
-        <v>20</v>
-      </c>
-      <c r="X2" s="4">
-        <v>15</v>
-      </c>
-      <c r="Y2" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T3" s="4">
-        <v>2</v>
-      </c>
-      <c r="U3" s="4">
-        <v>799</v>
-      </c>
-      <c r="V3" s="4">
-        <v>350</v>
-      </c>
-      <c r="W3" s="4">
+      <c r="T4" s="4">
+        <v>499</v>
+      </c>
+      <c r="U4" s="4">
+        <v>150</v>
+      </c>
+      <c r="V4" s="4">
         <v>30</v>
       </c>
-      <c r="X3" s="4">
+      <c r="W4" s="4">
         <v>25</v>
       </c>
-      <c r="Y3" s="4">
+      <c r="X4" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T4" s="4">
-        <v>1</v>
-      </c>
-      <c r="U4" s="4">
-        <v>499</v>
-      </c>
-      <c r="V4" s="4">
-        <v>150</v>
-      </c>
-      <c r="W4" s="4">
-        <v>30</v>
-      </c>
-      <c r="X4" s="4">
-        <v>25</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
@@ -1306,17 +1277,16 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="6"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="4"/>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1333,17 +1303,16 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="6"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
@@ -1360,17 +1329,16 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="6"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
@@ -1387,17 +1355,16 @@
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="6"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
@@ -1414,17 +1381,16 @@
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="6"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="4"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
@@ -1441,17 +1407,16 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="6"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
@@ -1468,17 +1433,16 @@
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="6"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="4"/>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
@@ -1495,17 +1459,16 @@
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="6"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="4"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -1522,17 +1485,16 @@
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="6"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
@@ -1549,17 +1511,16 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="6"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
@@ -1576,17 +1537,16 @@
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="6"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="4"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
@@ -1603,17 +1563,16 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="6"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="4"/>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
@@ -1630,17 +1589,16 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="6"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="4"/>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
@@ -1657,17 +1615,16 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="6"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="4"/>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
@@ -1684,17 +1641,16 @@
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="6"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="4"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
@@ -1711,17 +1667,16 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="6"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="4"/>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
@@ -1738,17 +1693,16 @@
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="6"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="4"/>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
@@ -1765,17 +1719,16 @@
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="6"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="4"/>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
@@ -1792,17 +1745,16 @@
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="6"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="4"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
-      <c r="Y23" s="4"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
@@ -1819,17 +1771,16 @@
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="6"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="4"/>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
-      <c r="Y24" s="4"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
@@ -1846,17 +1797,16 @@
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="6"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="4"/>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
@@ -1873,17 +1823,16 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="6"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="4"/>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
@@ -1900,17 +1849,16 @@
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="6"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="4"/>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
       <c r="X27" s="4"/>
-      <c r="Y27" s="4"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
@@ -1927,17 +1875,16 @@
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="6"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
       <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
@@ -1954,17 +1901,16 @@
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="6"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="4"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
       <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
@@ -1981,17 +1927,16 @@
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="6"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="4"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
       <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
@@ -2008,17 +1953,16 @@
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="6"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="4"/>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
       <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
@@ -2035,17 +1979,16 @@
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="6"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="4"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
       <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
@@ -2062,17 +2005,16 @@
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="6"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="4"/>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
       <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
@@ -2089,17 +2031,16 @@
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="6"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
@@ -2116,17 +2057,16 @@
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="6"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="4"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
       <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
@@ -2143,17 +2083,16 @@
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="6"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="4"/>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
       <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
@@ -2170,17 +2109,16 @@
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="6"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="4"/>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
@@ -2197,17 +2135,16 @@
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="6"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="4"/>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
@@ -2224,17 +2161,16 @@
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="6"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="4"/>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -2251,17 +2187,16 @@
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="6"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="4"/>
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -2278,17 +2213,16 @@
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="6"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="4"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
@@ -2305,17 +2239,16 @@
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="6"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="4"/>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
@@ -2332,17 +2265,16 @@
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="6"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="4"/>
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
-      <c r="Y43" s="4"/>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
@@ -2359,17 +2291,16 @@
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="6"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="4"/>
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
-      <c r="Y44" s="4"/>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
@@ -2386,17 +2317,16 @@
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="6"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="6"/>
+      <c r="S45" s="4"/>
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
-      <c r="Y45" s="4"/>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
@@ -2413,17 +2343,16 @@
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="6"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="4"/>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
@@ -2440,17 +2369,16 @@
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="6"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="4"/>
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
-      <c r="Y47" s="4"/>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
@@ -2467,17 +2395,16 @@
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="6"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="4"/>
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
@@ -2494,17 +2421,16 @@
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="6"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="6"/>
+      <c r="S49" s="4"/>
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
@@ -2521,17 +2447,16 @@
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="6"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="4"/>
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
@@ -2548,17 +2473,16 @@
       <c r="N51" s="5"/>
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="6"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="6"/>
+      <c r="S51" s="4"/>
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
       <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="4"/>
       <c r="C52" s="5"/>
@@ -2575,17 +2499,16 @@
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="6"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="6"/>
+      <c r="S52" s="4"/>
       <c r="T52" s="4"/>
       <c r="U52" s="4"/>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
       <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
@@ -2602,17 +2525,16 @@
       <c r="N53" s="5"/>
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
-      <c r="Q53" s="5"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="6"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="6"/>
+      <c r="S53" s="4"/>
       <c r="T53" s="4"/>
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
       <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
@@ -2629,17 +2551,16 @@
       <c r="N54" s="5"/>
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="6"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="4"/>
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
       <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
@@ -2656,17 +2577,16 @@
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
-      <c r="Q55" s="5"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="6"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="4"/>
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
       <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
@@ -2683,17 +2603,16 @@
       <c r="N56" s="5"/>
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
-      <c r="Q56" s="5"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="6"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="4"/>
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
       <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
@@ -2710,17 +2629,16 @@
       <c r="N57" s="5"/>
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
-      <c r="Q57" s="5"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="6"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="4"/>
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
       <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
@@ -2737,17 +2655,16 @@
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="6"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="4"/>
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
       <c r="X58" s="4"/>
-      <c r="Y58" s="4"/>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
@@ -2764,17 +2681,16 @@
       <c r="N59" s="5"/>
       <c r="O59" s="5"/>
       <c r="P59" s="5"/>
-      <c r="Q59" s="5"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="6"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="4"/>
       <c r="T59" s="4"/>
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
-      <c r="Y59" s="4"/>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
@@ -2791,17 +2707,16 @@
       <c r="N60" s="5"/>
       <c r="O60" s="5"/>
       <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="4"/>
-      <c r="S60" s="6"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="4"/>
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
-      <c r="Y60" s="4"/>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="4"/>
       <c r="C61" s="5"/>
@@ -2818,17 +2733,16 @@
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
       <c r="P61" s="5"/>
-      <c r="Q61" s="5"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="6"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="4"/>
       <c r="T61" s="4"/>
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
@@ -2845,17 +2759,16 @@
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="6"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="4"/>
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
-      <c r="Y62" s="4"/>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
@@ -2872,17 +2785,16 @@
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
-      <c r="Q63" s="5"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="6"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="4"/>
       <c r="T63" s="4"/>
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
-      <c r="Y63" s="4"/>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="4"/>
       <c r="C64" s="5"/>
@@ -2899,17 +2811,16 @@
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="6"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="4"/>
       <c r="T64" s="4"/>
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
-      <c r="Y64" s="4"/>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
@@ -2926,17 +2837,16 @@
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="6"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="6"/>
+      <c r="S65" s="4"/>
       <c r="T65" s="4"/>
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="4"/>
       <c r="C66" s="5"/>
@@ -2953,17 +2863,16 @@
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="6"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="4"/>
       <c r="T66" s="4"/>
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="4"/>
       <c r="C67" s="5"/>
@@ -2980,17 +2889,16 @@
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
-      <c r="Q67" s="5"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="6"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="4"/>
       <c r="T67" s="4"/>
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="4"/>
       <c r="C68" s="5"/>
@@ -3007,17 +2915,16 @@
       <c r="N68" s="5"/>
       <c r="O68" s="5"/>
       <c r="P68" s="5"/>
-      <c r="Q68" s="5"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="6"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="4"/>
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
-      <c r="Y68" s="4"/>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="4"/>
       <c r="C69" s="5"/>
@@ -3034,17 +2941,16 @@
       <c r="N69" s="5"/>
       <c r="O69" s="5"/>
       <c r="P69" s="5"/>
-      <c r="Q69" s="5"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="6"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="6"/>
+      <c r="S69" s="4"/>
       <c r="T69" s="4"/>
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
       <c r="W69" s="4"/>
       <c r="X69" s="4"/>
-      <c r="Y69" s="4"/>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="4"/>
       <c r="C70" s="5"/>
@@ -3061,17 +2967,16 @@
       <c r="N70" s="5"/>
       <c r="O70" s="5"/>
       <c r="P70" s="5"/>
-      <c r="Q70" s="5"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="6"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="4"/>
       <c r="T70" s="4"/>
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
-      <c r="Y70" s="4"/>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="4"/>
       <c r="C71" s="5"/>
@@ -3088,17 +2993,16 @@
       <c r="N71" s="5"/>
       <c r="O71" s="5"/>
       <c r="P71" s="5"/>
-      <c r="Q71" s="5"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="6"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="6"/>
+      <c r="S71" s="4"/>
       <c r="T71" s="4"/>
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
       <c r="W71" s="4"/>
       <c r="X71" s="4"/>
-      <c r="Y71" s="4"/>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="4"/>
       <c r="C72" s="5"/>
@@ -3115,17 +3019,16 @@
       <c r="N72" s="5"/>
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
-      <c r="Q72" s="5"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="6"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="4"/>
       <c r="T72" s="4"/>
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
       <c r="W72" s="4"/>
       <c r="X72" s="4"/>
-      <c r="Y72" s="4"/>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="4"/>
       <c r="C73" s="5"/>
@@ -3142,17 +3045,16 @@
       <c r="N73" s="5"/>
       <c r="O73" s="5"/>
       <c r="P73" s="5"/>
-      <c r="Q73" s="5"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="6"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="6"/>
+      <c r="S73" s="4"/>
       <c r="T73" s="4"/>
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
       <c r="W73" s="4"/>
       <c r="X73" s="4"/>
-      <c r="Y73" s="4"/>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="4"/>
       <c r="C74" s="5"/>
@@ -3169,17 +3071,16 @@
       <c r="N74" s="5"/>
       <c r="O74" s="5"/>
       <c r="P74" s="5"/>
-      <c r="Q74" s="5"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="6"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="4"/>
       <c r="T74" s="4"/>
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
       <c r="W74" s="4"/>
       <c r="X74" s="4"/>
-      <c r="Y74" s="4"/>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="4"/>
       <c r="C75" s="5"/>
@@ -3196,17 +3097,16 @@
       <c r="N75" s="5"/>
       <c r="O75" s="5"/>
       <c r="P75" s="5"/>
-      <c r="Q75" s="5"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="6"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="6"/>
+      <c r="S75" s="4"/>
       <c r="T75" s="4"/>
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
       <c r="W75" s="4"/>
       <c r="X75" s="4"/>
-      <c r="Y75" s="4"/>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="4"/>
       <c r="C76" s="5"/>
@@ -3223,17 +3123,16 @@
       <c r="N76" s="5"/>
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="6"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="4"/>
       <c r="T76" s="4"/>
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
       <c r="W76" s="4"/>
       <c r="X76" s="4"/>
-      <c r="Y76" s="4"/>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="4"/>
       <c r="C77" s="5"/>
@@ -3250,17 +3149,16 @@
       <c r="N77" s="5"/>
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
-      <c r="Q77" s="5"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="6"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="6"/>
+      <c r="S77" s="4"/>
       <c r="T77" s="4"/>
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
       <c r="W77" s="4"/>
       <c r="X77" s="4"/>
-      <c r="Y77" s="4"/>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="4"/>
       <c r="C78" s="5"/>
@@ -3277,17 +3175,16 @@
       <c r="N78" s="5"/>
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
-      <c r="Q78" s="5"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="6"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="4"/>
       <c r="T78" s="4"/>
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
       <c r="W78" s="4"/>
       <c r="X78" s="4"/>
-      <c r="Y78" s="4"/>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="4"/>
       <c r="C79" s="5"/>
@@ -3304,17 +3201,16 @@
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
-      <c r="Q79" s="5"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="6"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="6"/>
+      <c r="S79" s="4"/>
       <c r="T79" s="4"/>
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
       <c r="W79" s="4"/>
       <c r="X79" s="4"/>
-      <c r="Y79" s="4"/>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
       <c r="B80" s="4"/>
       <c r="C80" s="5"/>
@@ -3331,17 +3227,16 @@
       <c r="N80" s="5"/>
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
-      <c r="Q80" s="5"/>
-      <c r="R80" s="4"/>
-      <c r="S80" s="6"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="4"/>
       <c r="T80" s="4"/>
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
       <c r="W80" s="4"/>
       <c r="X80" s="4"/>
-      <c r="Y80" s="4"/>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
       <c r="B81" s="4"/>
       <c r="C81" s="5"/>
@@ -3358,17 +3253,16 @@
       <c r="N81" s="5"/>
       <c r="O81" s="5"/>
       <c r="P81" s="5"/>
-      <c r="Q81" s="5"/>
-      <c r="R81" s="4"/>
-      <c r="S81" s="6"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="6"/>
+      <c r="S81" s="4"/>
       <c r="T81" s="4"/>
       <c r="U81" s="4"/>
       <c r="V81" s="4"/>
       <c r="W81" s="4"/>
       <c r="X81" s="4"/>
-      <c r="Y81" s="4"/>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="B82" s="4"/>
       <c r="C82" s="5"/>
@@ -3385,17 +3279,16 @@
       <c r="N82" s="5"/>
       <c r="O82" s="5"/>
       <c r="P82" s="5"/>
-      <c r="Q82" s="5"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="6"/>
+      <c r="Q82" s="4"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="4"/>
       <c r="T82" s="4"/>
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
       <c r="W82" s="4"/>
       <c r="X82" s="4"/>
-      <c r="Y82" s="4"/>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="4"/>
       <c r="C83" s="5"/>
@@ -3412,17 +3305,16 @@
       <c r="N83" s="5"/>
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
-      <c r="Q83" s="5"/>
-      <c r="R83" s="4"/>
-      <c r="S83" s="6"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="6"/>
+      <c r="S83" s="4"/>
       <c r="T83" s="4"/>
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
       <c r="W83" s="4"/>
       <c r="X83" s="4"/>
-      <c r="Y83" s="4"/>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="4"/>
       <c r="C84" s="5"/>
@@ -3439,17 +3331,16 @@
       <c r="N84" s="5"/>
       <c r="O84" s="5"/>
       <c r="P84" s="5"/>
-      <c r="Q84" s="5"/>
-      <c r="R84" s="4"/>
-      <c r="S84" s="6"/>
+      <c r="Q84" s="4"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="4"/>
       <c r="T84" s="4"/>
       <c r="U84" s="4"/>
       <c r="V84" s="4"/>
       <c r="W84" s="4"/>
       <c r="X84" s="4"/>
-      <c r="Y84" s="4"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="4"/>
       <c r="C85" s="5"/>
@@ -3466,17 +3357,16 @@
       <c r="N85" s="5"/>
       <c r="O85" s="5"/>
       <c r="P85" s="5"/>
-      <c r="Q85" s="5"/>
-      <c r="R85" s="4"/>
-      <c r="S85" s="6"/>
+      <c r="Q85" s="4"/>
+      <c r="R85" s="6"/>
+      <c r="S85" s="4"/>
       <c r="T85" s="4"/>
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
       <c r="W85" s="4"/>
       <c r="X85" s="4"/>
-      <c r="Y85" s="4"/>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="4"/>
       <c r="C86" s="5"/>
@@ -3493,17 +3383,16 @@
       <c r="N86" s="5"/>
       <c r="O86" s="5"/>
       <c r="P86" s="5"/>
-      <c r="Q86" s="5"/>
-      <c r="R86" s="4"/>
-      <c r="S86" s="6"/>
+      <c r="Q86" s="4"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="4"/>
       <c r="T86" s="4"/>
       <c r="U86" s="4"/>
       <c r="V86" s="4"/>
       <c r="W86" s="4"/>
       <c r="X86" s="4"/>
-      <c r="Y86" s="4"/>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
       <c r="B87" s="4"/>
       <c r="C87" s="5"/>
@@ -3520,17 +3409,16 @@
       <c r="N87" s="5"/>
       <c r="O87" s="5"/>
       <c r="P87" s="5"/>
-      <c r="Q87" s="5"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="6"/>
+      <c r="Q87" s="4"/>
+      <c r="R87" s="6"/>
+      <c r="S87" s="4"/>
       <c r="T87" s="4"/>
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
       <c r="W87" s="4"/>
       <c r="X87" s="4"/>
-      <c r="Y87" s="4"/>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
       <c r="B88" s="4"/>
       <c r="C88" s="5"/>
@@ -3547,17 +3435,16 @@
       <c r="N88" s="5"/>
       <c r="O88" s="5"/>
       <c r="P88" s="5"/>
-      <c r="Q88" s="5"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="6"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="4"/>
       <c r="T88" s="4"/>
       <c r="U88" s="4"/>
       <c r="V88" s="4"/>
       <c r="W88" s="4"/>
       <c r="X88" s="4"/>
-      <c r="Y88" s="4"/>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
       <c r="B89" s="4"/>
       <c r="C89" s="5"/>
@@ -3574,17 +3461,16 @@
       <c r="N89" s="5"/>
       <c r="O89" s="5"/>
       <c r="P89" s="5"/>
-      <c r="Q89" s="5"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="6"/>
+      <c r="Q89" s="4"/>
+      <c r="R89" s="6"/>
+      <c r="S89" s="4"/>
       <c r="T89" s="4"/>
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
       <c r="X89" s="4"/>
-      <c r="Y89" s="4"/>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="4"/>
       <c r="C90" s="5"/>
@@ -3601,17 +3487,16 @@
       <c r="N90" s="5"/>
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
-      <c r="Q90" s="5"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="6"/>
+      <c r="Q90" s="4"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="4"/>
       <c r="T90" s="4"/>
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
       <c r="W90" s="4"/>
       <c r="X90" s="4"/>
-      <c r="Y90" s="4"/>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
       <c r="B91" s="4"/>
       <c r="C91" s="5"/>
@@ -3628,17 +3513,16 @@
       <c r="N91" s="5"/>
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
-      <c r="Q91" s="5"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="6"/>
+      <c r="Q91" s="4"/>
+      <c r="R91" s="6"/>
+      <c r="S91" s="4"/>
       <c r="T91" s="4"/>
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
       <c r="W91" s="4"/>
       <c r="X91" s="4"/>
-      <c r="Y91" s="4"/>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
       <c r="B92" s="4"/>
       <c r="C92" s="5"/>
@@ -3655,17 +3539,16 @@
       <c r="N92" s="5"/>
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
-      <c r="Q92" s="5"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="6"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="4"/>
       <c r="T92" s="4"/>
       <c r="U92" s="4"/>
       <c r="V92" s="4"/>
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
       <c r="B93" s="4"/>
       <c r="C93" s="5"/>
@@ -3682,17 +3565,16 @@
       <c r="N93" s="5"/>
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
-      <c r="Q93" s="5"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="6"/>
+      <c r="Q93" s="4"/>
+      <c r="R93" s="6"/>
+      <c r="S93" s="4"/>
       <c r="T93" s="4"/>
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
       <c r="W93" s="4"/>
       <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
       <c r="B94" s="4"/>
       <c r="C94" s="5"/>
@@ -3709,17 +3591,16 @@
       <c r="N94" s="5"/>
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
-      <c r="Q94" s="5"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="6"/>
+      <c r="Q94" s="4"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="4"/>
       <c r="T94" s="4"/>
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
       <c r="W94" s="4"/>
       <c r="X94" s="4"/>
-      <c r="Y94" s="4"/>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
       <c r="B95" s="4"/>
       <c r="C95" s="5"/>
@@ -3736,17 +3617,16 @@
       <c r="N95" s="5"/>
       <c r="O95" s="5"/>
       <c r="P95" s="5"/>
-      <c r="Q95" s="5"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="6"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="6"/>
+      <c r="S95" s="4"/>
       <c r="T95" s="4"/>
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
-      <c r="Y95" s="4"/>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="B96" s="4"/>
       <c r="C96" s="5"/>
@@ -3763,17 +3643,16 @@
       <c r="N96" s="5"/>
       <c r="O96" s="5"/>
       <c r="P96" s="5"/>
-      <c r="Q96" s="5"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="6"/>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="4"/>
       <c r="T96" s="4"/>
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
       <c r="W96" s="4"/>
       <c r="X96" s="4"/>
-      <c r="Y96" s="4"/>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
       <c r="B97" s="4"/>
       <c r="C97" s="5"/>
@@ -3790,17 +3669,16 @@
       <c r="N97" s="5"/>
       <c r="O97" s="5"/>
       <c r="P97" s="5"/>
-      <c r="Q97" s="5"/>
-      <c r="R97" s="4"/>
-      <c r="S97" s="6"/>
+      <c r="Q97" s="4"/>
+      <c r="R97" s="6"/>
+      <c r="S97" s="4"/>
       <c r="T97" s="4"/>
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
       <c r="W97" s="4"/>
       <c r="X97" s="4"/>
-      <c r="Y97" s="4"/>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="4"/>
       <c r="C98" s="5"/>
@@ -3817,17 +3695,16 @@
       <c r="N98" s="5"/>
       <c r="O98" s="5"/>
       <c r="P98" s="5"/>
-      <c r="Q98" s="5"/>
-      <c r="R98" s="4"/>
-      <c r="S98" s="6"/>
+      <c r="Q98" s="4"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="4"/>
       <c r="T98" s="4"/>
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
       <c r="W98" s="4"/>
       <c r="X98" s="4"/>
-      <c r="Y98" s="4"/>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="4"/>
       <c r="C99" s="5"/>
@@ -3844,17 +3721,16 @@
       <c r="N99" s="5"/>
       <c r="O99" s="5"/>
       <c r="P99" s="5"/>
-      <c r="Q99" s="5"/>
-      <c r="R99" s="4"/>
-      <c r="S99" s="6"/>
+      <c r="Q99" s="4"/>
+      <c r="R99" s="6"/>
+      <c r="S99" s="4"/>
       <c r="T99" s="4"/>
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
       <c r="W99" s="4"/>
       <c r="X99" s="4"/>
-      <c r="Y99" s="4"/>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="B100" s="4"/>
       <c r="C100" s="5"/>
@@ -3871,17 +3747,16 @@
       <c r="N100" s="5"/>
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
-      <c r="Q100" s="5"/>
-      <c r="R100" s="4"/>
-      <c r="S100" s="6"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="4"/>
       <c r="T100" s="4"/>
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
       <c r="W100" s="4"/>
       <c r="X100" s="4"/>
-      <c r="Y100" s="4"/>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
       <c r="B101" s="4"/>
       <c r="C101" s="5"/>
@@ -3898,17 +3773,16 @@
       <c r="N101" s="5"/>
       <c r="O101" s="5"/>
       <c r="P101" s="5"/>
-      <c r="Q101" s="5"/>
-      <c r="R101" s="4"/>
-      <c r="S101" s="6"/>
+      <c r="Q101" s="4"/>
+      <c r="R101" s="6"/>
+      <c r="S101" s="4"/>
       <c r="T101" s="4"/>
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
       <c r="W101" s="4"/>
       <c r="X101" s="4"/>
-      <c r="Y101" s="4"/>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
       <c r="B102" s="4"/>
       <c r="C102" s="5"/>
@@ -3925,17 +3799,16 @@
       <c r="N102" s="5"/>
       <c r="O102" s="5"/>
       <c r="P102" s="5"/>
-      <c r="Q102" s="5"/>
-      <c r="R102" s="4"/>
-      <c r="S102" s="6"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="4"/>
       <c r="T102" s="4"/>
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
       <c r="W102" s="4"/>
       <c r="X102" s="4"/>
-      <c r="Y102" s="4"/>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="4"/>
       <c r="C103" s="5"/>
@@ -3952,17 +3825,16 @@
       <c r="N103" s="5"/>
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
-      <c r="Q103" s="5"/>
-      <c r="R103" s="4"/>
-      <c r="S103" s="6"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="6"/>
+      <c r="S103" s="4"/>
       <c r="T103" s="4"/>
       <c r="U103" s="4"/>
       <c r="V103" s="4"/>
       <c r="W103" s="4"/>
       <c r="X103" s="4"/>
-      <c r="Y103" s="4"/>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="4"/>
       <c r="C104" s="5"/>
@@ -3979,17 +3851,16 @@
       <c r="N104" s="5"/>
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
-      <c r="Q104" s="5"/>
-      <c r="R104" s="4"/>
-      <c r="S104" s="6"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="4"/>
       <c r="T104" s="4"/>
       <c r="U104" s="4"/>
       <c r="V104" s="4"/>
       <c r="W104" s="4"/>
       <c r="X104" s="4"/>
-      <c r="Y104" s="4"/>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="4"/>
       <c r="C105" s="5"/>
@@ -4006,17 +3877,16 @@
       <c r="N105" s="5"/>
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
-      <c r="Q105" s="5"/>
-      <c r="R105" s="4"/>
-      <c r="S105" s="6"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="6"/>
+      <c r="S105" s="4"/>
       <c r="T105" s="4"/>
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
       <c r="W105" s="4"/>
       <c r="X105" s="4"/>
-      <c r="Y105" s="4"/>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
       <c r="B106" s="4"/>
       <c r="C106" s="5"/>
@@ -4033,17 +3903,16 @@
       <c r="N106" s="5"/>
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
-      <c r="Q106" s="5"/>
-      <c r="R106" s="4"/>
-      <c r="S106" s="6"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="4"/>
       <c r="T106" s="4"/>
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
       <c r="W106" s="4"/>
       <c r="X106" s="4"/>
-      <c r="Y106" s="4"/>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
       <c r="B107" s="4"/>
       <c r="C107" s="5"/>
@@ -4060,17 +3929,16 @@
       <c r="N107" s="5"/>
       <c r="O107" s="5"/>
       <c r="P107" s="5"/>
-      <c r="Q107" s="5"/>
-      <c r="R107" s="4"/>
-      <c r="S107" s="6"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="6"/>
+      <c r="S107" s="4"/>
       <c r="T107" s="4"/>
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
       <c r="W107" s="4"/>
       <c r="X107" s="4"/>
-      <c r="Y107" s="4"/>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
       <c r="B108" s="4"/>
       <c r="C108" s="5"/>
@@ -4087,17 +3955,16 @@
       <c r="N108" s="5"/>
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
-      <c r="Q108" s="5"/>
-      <c r="R108" s="4"/>
-      <c r="S108" s="6"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="4"/>
       <c r="T108" s="4"/>
       <c r="U108" s="4"/>
       <c r="V108" s="4"/>
       <c r="W108" s="4"/>
       <c r="X108" s="4"/>
-      <c r="Y108" s="4"/>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
       <c r="B109" s="4"/>
       <c r="C109" s="5"/>
@@ -4114,17 +3981,16 @@
       <c r="N109" s="5"/>
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
-      <c r="Q109" s="5"/>
-      <c r="R109" s="4"/>
-      <c r="S109" s="6"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="6"/>
+      <c r="S109" s="4"/>
       <c r="T109" s="4"/>
       <c r="U109" s="4"/>
       <c r="V109" s="4"/>
       <c r="W109" s="4"/>
       <c r="X109" s="4"/>
-      <c r="Y109" s="4"/>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
       <c r="B110" s="4"/>
       <c r="C110" s="5"/>
@@ -4141,17 +4007,16 @@
       <c r="N110" s="5"/>
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
-      <c r="Q110" s="5"/>
-      <c r="R110" s="4"/>
-      <c r="S110" s="6"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="4"/>
       <c r="T110" s="4"/>
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
       <c r="W110" s="4"/>
       <c r="X110" s="4"/>
-      <c r="Y110" s="4"/>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="B111" s="4"/>
       <c r="C111" s="5"/>
@@ -4168,17 +4033,16 @@
       <c r="N111" s="5"/>
       <c r="O111" s="5"/>
       <c r="P111" s="5"/>
-      <c r="Q111" s="5"/>
-      <c r="R111" s="4"/>
-      <c r="S111" s="6"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="6"/>
+      <c r="S111" s="4"/>
       <c r="T111" s="4"/>
       <c r="U111" s="4"/>
       <c r="V111" s="4"/>
       <c r="W111" s="4"/>
       <c r="X111" s="4"/>
-      <c r="Y111" s="4"/>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
       <c r="B112" s="4"/>
       <c r="C112" s="5"/>
@@ -4195,17 +4059,16 @@
       <c r="N112" s="5"/>
       <c r="O112" s="5"/>
       <c r="P112" s="5"/>
-      <c r="Q112" s="5"/>
-      <c r="R112" s="4"/>
-      <c r="S112" s="6"/>
+      <c r="Q112" s="4"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="4"/>
       <c r="T112" s="4"/>
       <c r="U112" s="4"/>
       <c r="V112" s="4"/>
       <c r="W112" s="4"/>
       <c r="X112" s="4"/>
-      <c r="Y112" s="4"/>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
       <c r="B113" s="4"/>
       <c r="C113" s="5"/>
@@ -4222,17 +4085,16 @@
       <c r="N113" s="5"/>
       <c r="O113" s="5"/>
       <c r="P113" s="5"/>
-      <c r="Q113" s="5"/>
-      <c r="R113" s="4"/>
-      <c r="S113" s="6"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="6"/>
+      <c r="S113" s="4"/>
       <c r="T113" s="4"/>
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
       <c r="W113" s="4"/>
       <c r="X113" s="4"/>
-      <c r="Y113" s="4"/>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="B114" s="4"/>
       <c r="C114" s="5"/>
@@ -4249,17 +4111,16 @@
       <c r="N114" s="5"/>
       <c r="O114" s="5"/>
       <c r="P114" s="5"/>
-      <c r="Q114" s="5"/>
-      <c r="R114" s="4"/>
-      <c r="S114" s="6"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="4"/>
       <c r="T114" s="4"/>
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
       <c r="W114" s="4"/>
       <c r="X114" s="4"/>
-      <c r="Y114" s="4"/>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
       <c r="B115" s="4"/>
       <c r="C115" s="5"/>
@@ -4276,17 +4137,16 @@
       <c r="N115" s="5"/>
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
-      <c r="Q115" s="5"/>
-      <c r="R115" s="4"/>
-      <c r="S115" s="6"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="6"/>
+      <c r="S115" s="4"/>
       <c r="T115" s="4"/>
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
       <c r="W115" s="4"/>
       <c r="X115" s="4"/>
-      <c r="Y115" s="4"/>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
       <c r="B116" s="4"/>
       <c r="C116" s="5"/>
@@ -4303,17 +4163,16 @@
       <c r="N116" s="5"/>
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
-      <c r="Q116" s="5"/>
-      <c r="R116" s="4"/>
-      <c r="S116" s="6"/>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="4"/>
       <c r="T116" s="4"/>
       <c r="U116" s="4"/>
       <c r="V116" s="4"/>
       <c r="W116" s="4"/>
       <c r="X116" s="4"/>
-      <c r="Y116" s="4"/>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
       <c r="B117" s="4"/>
       <c r="C117" s="5"/>
@@ -4330,17 +4189,16 @@
       <c r="N117" s="5"/>
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
-      <c r="Q117" s="5"/>
-      <c r="R117" s="4"/>
-      <c r="S117" s="6"/>
+      <c r="Q117" s="4"/>
+      <c r="R117" s="6"/>
+      <c r="S117" s="4"/>
       <c r="T117" s="4"/>
       <c r="U117" s="4"/>
       <c r="V117" s="4"/>
       <c r="W117" s="4"/>
       <c r="X117" s="4"/>
-      <c r="Y117" s="4"/>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="B118" s="4"/>
       <c r="C118" s="5"/>
@@ -4357,17 +4215,16 @@
       <c r="N118" s="5"/>
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
-      <c r="Q118" s="5"/>
-      <c r="R118" s="4"/>
-      <c r="S118" s="6"/>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="4"/>
       <c r="T118" s="4"/>
       <c r="U118" s="4"/>
       <c r="V118" s="4"/>
       <c r="W118" s="4"/>
       <c r="X118" s="4"/>
-      <c r="Y118" s="4"/>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
       <c r="B119" s="4"/>
       <c r="C119" s="5"/>
@@ -4384,17 +4241,16 @@
       <c r="N119" s="5"/>
       <c r="O119" s="5"/>
       <c r="P119" s="5"/>
-      <c r="Q119" s="5"/>
-      <c r="R119" s="4"/>
-      <c r="S119" s="6"/>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="6"/>
+      <c r="S119" s="4"/>
       <c r="T119" s="4"/>
       <c r="U119" s="4"/>
       <c r="V119" s="4"/>
       <c r="W119" s="4"/>
       <c r="X119" s="4"/>
-      <c r="Y119" s="4"/>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
       <c r="B120" s="4"/>
       <c r="C120" s="5"/>
@@ -4411,17 +4267,16 @@
       <c r="N120" s="5"/>
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
-      <c r="Q120" s="5"/>
-      <c r="R120" s="4"/>
-      <c r="S120" s="6"/>
+      <c r="Q120" s="4"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="4"/>
       <c r="T120" s="4"/>
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
       <c r="W120" s="4"/>
       <c r="X120" s="4"/>
-      <c r="Y120" s="4"/>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
       <c r="B121" s="4"/>
       <c r="C121" s="5"/>
@@ -4438,17 +4293,16 @@
       <c r="N121" s="5"/>
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
-      <c r="Q121" s="5"/>
-      <c r="R121" s="4"/>
-      <c r="S121" s="6"/>
+      <c r="Q121" s="4"/>
+      <c r="R121" s="6"/>
+      <c r="S121" s="4"/>
       <c r="T121" s="4"/>
       <c r="U121" s="4"/>
       <c r="V121" s="4"/>
       <c r="W121" s="4"/>
       <c r="X121" s="4"/>
-      <c r="Y121" s="4"/>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="B122" s="4"/>
       <c r="C122" s="5"/>
@@ -4465,17 +4319,16 @@
       <c r="N122" s="5"/>
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
-      <c r="Q122" s="5"/>
-      <c r="R122" s="4"/>
-      <c r="S122" s="6"/>
+      <c r="Q122" s="4"/>
+      <c r="R122" s="6"/>
+      <c r="S122" s="4"/>
       <c r="T122" s="4"/>
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
       <c r="W122" s="4"/>
       <c r="X122" s="4"/>
-      <c r="Y122" s="4"/>
-    </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
       <c r="B123" s="4"/>
       <c r="C123" s="5"/>
@@ -4492,17 +4345,16 @@
       <c r="N123" s="5"/>
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
-      <c r="Q123" s="5"/>
-      <c r="R123" s="4"/>
-      <c r="S123" s="6"/>
+      <c r="Q123" s="4"/>
+      <c r="R123" s="6"/>
+      <c r="S123" s="4"/>
       <c r="T123" s="4"/>
       <c r="U123" s="4"/>
       <c r="V123" s="4"/>
       <c r="W123" s="4"/>
       <c r="X123" s="4"/>
-      <c r="Y123" s="4"/>
-    </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
       <c r="B124" s="4"/>
       <c r="C124" s="5"/>
@@ -4519,17 +4371,16 @@
       <c r="N124" s="5"/>
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
-      <c r="Q124" s="5"/>
-      <c r="R124" s="4"/>
-      <c r="S124" s="6"/>
+      <c r="Q124" s="4"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="4"/>
       <c r="T124" s="4"/>
       <c r="U124" s="4"/>
       <c r="V124" s="4"/>
       <c r="W124" s="4"/>
       <c r="X124" s="4"/>
-      <c r="Y124" s="4"/>
-    </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
       <c r="B125" s="4"/>
       <c r="C125" s="5"/>
@@ -4546,17 +4397,16 @@
       <c r="N125" s="5"/>
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
-      <c r="Q125" s="5"/>
-      <c r="R125" s="4"/>
-      <c r="S125" s="6"/>
+      <c r="Q125" s="4"/>
+      <c r="R125" s="6"/>
+      <c r="S125" s="4"/>
       <c r="T125" s="4"/>
       <c r="U125" s="4"/>
       <c r="V125" s="4"/>
       <c r="W125" s="4"/>
       <c r="X125" s="4"/>
-      <c r="Y125" s="4"/>
-    </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
       <c r="B126" s="4"/>
       <c r="C126" s="5"/>
@@ -4573,17 +4423,16 @@
       <c r="N126" s="5"/>
       <c r="O126" s="5"/>
       <c r="P126" s="5"/>
-      <c r="Q126" s="5"/>
-      <c r="R126" s="4"/>
-      <c r="S126" s="6"/>
+      <c r="Q126" s="4"/>
+      <c r="R126" s="6"/>
+      <c r="S126" s="4"/>
       <c r="T126" s="4"/>
       <c r="U126" s="4"/>
       <c r="V126" s="4"/>
       <c r="W126" s="4"/>
       <c r="X126" s="4"/>
-      <c r="Y126" s="4"/>
-    </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
       <c r="B127" s="4"/>
       <c r="C127" s="5"/>
@@ -4600,17 +4449,16 @@
       <c r="N127" s="5"/>
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
-      <c r="Q127" s="5"/>
-      <c r="R127" s="4"/>
-      <c r="S127" s="6"/>
+      <c r="Q127" s="4"/>
+      <c r="R127" s="6"/>
+      <c r="S127" s="4"/>
       <c r="T127" s="4"/>
       <c r="U127" s="4"/>
       <c r="V127" s="4"/>
       <c r="W127" s="4"/>
       <c r="X127" s="4"/>
-      <c r="Y127" s="4"/>
-    </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
       <c r="B128" s="4"/>
       <c r="C128" s="5"/>
@@ -4627,17 +4475,16 @@
       <c r="N128" s="5"/>
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
-      <c r="Q128" s="5"/>
-      <c r="R128" s="4"/>
-      <c r="S128" s="6"/>
+      <c r="Q128" s="4"/>
+      <c r="R128" s="6"/>
+      <c r="S128" s="4"/>
       <c r="T128" s="4"/>
       <c r="U128" s="4"/>
       <c r="V128" s="4"/>
       <c r="W128" s="4"/>
       <c r="X128" s="4"/>
-      <c r="Y128" s="4"/>
-    </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
       <c r="B129" s="4"/>
       <c r="C129" s="5"/>
@@ -4654,17 +4501,16 @@
       <c r="N129" s="5"/>
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
-      <c r="Q129" s="5"/>
-      <c r="R129" s="4"/>
-      <c r="S129" s="6"/>
+      <c r="Q129" s="4"/>
+      <c r="R129" s="6"/>
+      <c r="S129" s="4"/>
       <c r="T129" s="4"/>
       <c r="U129" s="4"/>
       <c r="V129" s="4"/>
       <c r="W129" s="4"/>
       <c r="X129" s="4"/>
-      <c r="Y129" s="4"/>
-    </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
       <c r="B130" s="4"/>
       <c r="C130" s="5"/>
@@ -4681,17 +4527,16 @@
       <c r="N130" s="5"/>
       <c r="O130" s="5"/>
       <c r="P130" s="5"/>
-      <c r="Q130" s="5"/>
-      <c r="R130" s="4"/>
-      <c r="S130" s="6"/>
+      <c r="Q130" s="4"/>
+      <c r="R130" s="6"/>
+      <c r="S130" s="4"/>
       <c r="T130" s="4"/>
       <c r="U130" s="4"/>
       <c r="V130" s="4"/>
       <c r="W130" s="4"/>
       <c r="X130" s="4"/>
-      <c r="Y130" s="4"/>
-    </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
       <c r="B131" s="4"/>
       <c r="C131" s="5"/>
@@ -4708,17 +4553,16 @@
       <c r="N131" s="5"/>
       <c r="O131" s="5"/>
       <c r="P131" s="5"/>
-      <c r="Q131" s="5"/>
-      <c r="R131" s="4"/>
-      <c r="S131" s="6"/>
+      <c r="Q131" s="4"/>
+      <c r="R131" s="6"/>
+      <c r="S131" s="4"/>
       <c r="T131" s="4"/>
       <c r="U131" s="4"/>
       <c r="V131" s="4"/>
       <c r="W131" s="4"/>
       <c r="X131" s="4"/>
-      <c r="Y131" s="4"/>
-    </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
       <c r="B132" s="4"/>
       <c r="C132" s="5"/>
@@ -4735,17 +4579,16 @@
       <c r="N132" s="5"/>
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
-      <c r="Q132" s="5"/>
-      <c r="R132" s="4"/>
-      <c r="S132" s="6"/>
+      <c r="Q132" s="4"/>
+      <c r="R132" s="6"/>
+      <c r="S132" s="4"/>
       <c r="T132" s="4"/>
       <c r="U132" s="4"/>
       <c r="V132" s="4"/>
       <c r="W132" s="4"/>
       <c r="X132" s="4"/>
-      <c r="Y132" s="4"/>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
       <c r="B133" s="4"/>
       <c r="C133" s="5"/>
@@ -4762,17 +4605,16 @@
       <c r="N133" s="5"/>
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
-      <c r="Q133" s="5"/>
-      <c r="R133" s="4"/>
-      <c r="S133" s="6"/>
+      <c r="Q133" s="4"/>
+      <c r="R133" s="6"/>
+      <c r="S133" s="4"/>
       <c r="T133" s="4"/>
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
       <c r="W133" s="4"/>
       <c r="X133" s="4"/>
-      <c r="Y133" s="4"/>
-    </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" s="3"/>
       <c r="B134" s="4"/>
       <c r="C134" s="5"/>
@@ -4789,17 +4631,16 @@
       <c r="N134" s="5"/>
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
-      <c r="Q134" s="5"/>
-      <c r="R134" s="4"/>
-      <c r="S134" s="6"/>
+      <c r="Q134" s="4"/>
+      <c r="R134" s="6"/>
+      <c r="S134" s="4"/>
       <c r="T134" s="4"/>
       <c r="U134" s="4"/>
       <c r="V134" s="4"/>
       <c r="W134" s="4"/>
       <c r="X134" s="4"/>
-      <c r="Y134" s="4"/>
-    </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" s="3"/>
       <c r="B135" s="4"/>
       <c r="C135" s="5"/>
@@ -4816,17 +4657,16 @@
       <c r="N135" s="5"/>
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
-      <c r="Q135" s="5"/>
-      <c r="R135" s="4"/>
-      <c r="S135" s="6"/>
+      <c r="Q135" s="4"/>
+      <c r="R135" s="6"/>
+      <c r="S135" s="4"/>
       <c r="T135" s="4"/>
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
       <c r="W135" s="4"/>
       <c r="X135" s="4"/>
-      <c r="Y135" s="4"/>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" s="3"/>
       <c r="B136" s="4"/>
       <c r="C136" s="5"/>
@@ -4843,17 +4683,16 @@
       <c r="N136" s="5"/>
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
-      <c r="Q136" s="5"/>
-      <c r="R136" s="4"/>
-      <c r="S136" s="6"/>
+      <c r="Q136" s="4"/>
+      <c r="R136" s="6"/>
+      <c r="S136" s="4"/>
       <c r="T136" s="4"/>
       <c r="U136" s="4"/>
       <c r="V136" s="4"/>
       <c r="W136" s="4"/>
       <c r="X136" s="4"/>
-      <c r="Y136" s="4"/>
-    </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" s="3"/>
       <c r="B137" s="4"/>
       <c r="C137" s="5"/>
@@ -4870,17 +4709,16 @@
       <c r="N137" s="5"/>
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
-      <c r="Q137" s="5"/>
-      <c r="R137" s="4"/>
-      <c r="S137" s="6"/>
+      <c r="Q137" s="4"/>
+      <c r="R137" s="6"/>
+      <c r="S137" s="4"/>
       <c r="T137" s="4"/>
       <c r="U137" s="4"/>
       <c r="V137" s="4"/>
       <c r="W137" s="4"/>
       <c r="X137" s="4"/>
-      <c r="Y137" s="4"/>
-    </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" s="3"/>
       <c r="B138" s="4"/>
       <c r="C138" s="5"/>
@@ -4897,17 +4735,16 @@
       <c r="N138" s="5"/>
       <c r="O138" s="5"/>
       <c r="P138" s="5"/>
-      <c r="Q138" s="5"/>
-      <c r="R138" s="4"/>
-      <c r="S138" s="6"/>
+      <c r="Q138" s="4"/>
+      <c r="R138" s="6"/>
+      <c r="S138" s="4"/>
       <c r="T138" s="4"/>
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
       <c r="W138" s="4"/>
       <c r="X138" s="4"/>
-      <c r="Y138" s="4"/>
-    </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
       <c r="B139" s="4"/>
       <c r="C139" s="5"/>
@@ -4924,17 +4761,16 @@
       <c r="N139" s="5"/>
       <c r="O139" s="5"/>
       <c r="P139" s="5"/>
-      <c r="Q139" s="5"/>
-      <c r="R139" s="4"/>
-      <c r="S139" s="6"/>
+      <c r="Q139" s="4"/>
+      <c r="R139" s="6"/>
+      <c r="S139" s="4"/>
       <c r="T139" s="4"/>
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
       <c r="W139" s="4"/>
       <c r="X139" s="4"/>
-      <c r="Y139" s="4"/>
-    </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" s="3"/>
       <c r="B140" s="4"/>
       <c r="C140" s="5"/>
@@ -4951,17 +4787,16 @@
       <c r="N140" s="5"/>
       <c r="O140" s="5"/>
       <c r="P140" s="5"/>
-      <c r="Q140" s="5"/>
-      <c r="R140" s="4"/>
-      <c r="S140" s="6"/>
+      <c r="Q140" s="4"/>
+      <c r="R140" s="6"/>
+      <c r="S140" s="4"/>
       <c r="T140" s="4"/>
       <c r="U140" s="4"/>
       <c r="V140" s="4"/>
       <c r="W140" s="4"/>
       <c r="X140" s="4"/>
-      <c r="Y140" s="4"/>
-    </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" s="3"/>
       <c r="B141" s="4"/>
       <c r="C141" s="5"/>
@@ -4978,17 +4813,16 @@
       <c r="N141" s="5"/>
       <c r="O141" s="5"/>
       <c r="P141" s="5"/>
-      <c r="Q141" s="5"/>
-      <c r="R141" s="4"/>
-      <c r="S141" s="6"/>
+      <c r="Q141" s="4"/>
+      <c r="R141" s="6"/>
+      <c r="S141" s="4"/>
       <c r="T141" s="4"/>
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
       <c r="W141" s="4"/>
       <c r="X141" s="4"/>
-      <c r="Y141" s="4"/>
-    </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" s="3"/>
       <c r="B142" s="4"/>
       <c r="C142" s="5"/>
@@ -5005,17 +4839,16 @@
       <c r="N142" s="5"/>
       <c r="O142" s="5"/>
       <c r="P142" s="5"/>
-      <c r="Q142" s="5"/>
-      <c r="R142" s="4"/>
-      <c r="S142" s="6"/>
+      <c r="Q142" s="4"/>
+      <c r="R142" s="6"/>
+      <c r="S142" s="4"/>
       <c r="T142" s="4"/>
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
       <c r="W142" s="4"/>
       <c r="X142" s="4"/>
-      <c r="Y142" s="4"/>
-    </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" s="3"/>
       <c r="B143" s="4"/>
       <c r="C143" s="5"/>
@@ -5032,17 +4865,16 @@
       <c r="N143" s="5"/>
       <c r="O143" s="5"/>
       <c r="P143" s="5"/>
-      <c r="Q143" s="5"/>
-      <c r="R143" s="4"/>
-      <c r="S143" s="6"/>
+      <c r="Q143" s="4"/>
+      <c r="R143" s="6"/>
+      <c r="S143" s="4"/>
       <c r="T143" s="4"/>
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
       <c r="W143" s="4"/>
       <c r="X143" s="4"/>
-      <c r="Y143" s="4"/>
-    </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" s="3"/>
       <c r="B144" s="4"/>
       <c r="C144" s="5"/>
@@ -5059,17 +4891,16 @@
       <c r="N144" s="5"/>
       <c r="O144" s="5"/>
       <c r="P144" s="5"/>
-      <c r="Q144" s="5"/>
-      <c r="R144" s="4"/>
-      <c r="S144" s="6"/>
+      <c r="Q144" s="4"/>
+      <c r="R144" s="6"/>
+      <c r="S144" s="4"/>
       <c r="T144" s="4"/>
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
       <c r="W144" s="4"/>
       <c r="X144" s="4"/>
-      <c r="Y144" s="4"/>
-    </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" s="3"/>
       <c r="B145" s="4"/>
       <c r="C145" s="5"/>
@@ -5086,17 +4917,16 @@
       <c r="N145" s="5"/>
       <c r="O145" s="5"/>
       <c r="P145" s="5"/>
-      <c r="Q145" s="5"/>
-      <c r="R145" s="4"/>
-      <c r="S145" s="6"/>
+      <c r="Q145" s="4"/>
+      <c r="R145" s="6"/>
+      <c r="S145" s="4"/>
       <c r="T145" s="4"/>
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
       <c r="W145" s="4"/>
       <c r="X145" s="4"/>
-      <c r="Y145" s="4"/>
-    </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" s="3"/>
       <c r="B146" s="4"/>
       <c r="C146" s="5"/>
@@ -5113,17 +4943,16 @@
       <c r="N146" s="5"/>
       <c r="O146" s="5"/>
       <c r="P146" s="5"/>
-      <c r="Q146" s="5"/>
-      <c r="R146" s="4"/>
-      <c r="S146" s="6"/>
+      <c r="Q146" s="4"/>
+      <c r="R146" s="6"/>
+      <c r="S146" s="4"/>
       <c r="T146" s="4"/>
       <c r="U146" s="4"/>
       <c r="V146" s="4"/>
       <c r="W146" s="4"/>
       <c r="X146" s="4"/>
-      <c r="Y146" s="4"/>
-    </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" s="3"/>
       <c r="B147" s="4"/>
       <c r="C147" s="5"/>
@@ -5140,17 +4969,16 @@
       <c r="N147" s="5"/>
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
-      <c r="Q147" s="5"/>
-      <c r="R147" s="4"/>
-      <c r="S147" s="6"/>
+      <c r="Q147" s="4"/>
+      <c r="R147" s="6"/>
+      <c r="S147" s="4"/>
       <c r="T147" s="4"/>
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
       <c r="W147" s="4"/>
       <c r="X147" s="4"/>
-      <c r="Y147" s="4"/>
-    </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" s="3"/>
       <c r="B148" s="4"/>
       <c r="C148" s="5"/>
@@ -5167,17 +4995,16 @@
       <c r="N148" s="5"/>
       <c r="O148" s="5"/>
       <c r="P148" s="5"/>
-      <c r="Q148" s="5"/>
-      <c r="R148" s="4"/>
-      <c r="S148" s="6"/>
+      <c r="Q148" s="4"/>
+      <c r="R148" s="6"/>
+      <c r="S148" s="4"/>
       <c r="T148" s="4"/>
       <c r="U148" s="4"/>
       <c r="V148" s="4"/>
       <c r="W148" s="4"/>
       <c r="X148" s="4"/>
-      <c r="Y148" s="4"/>
-    </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" s="3"/>
       <c r="B149" s="4"/>
       <c r="C149" s="5"/>
@@ -5194,17 +5021,16 @@
       <c r="N149" s="5"/>
       <c r="O149" s="5"/>
       <c r="P149" s="5"/>
-      <c r="Q149" s="5"/>
-      <c r="R149" s="4"/>
-      <c r="S149" s="6"/>
+      <c r="Q149" s="4"/>
+      <c r="R149" s="6"/>
+      <c r="S149" s="4"/>
       <c r="T149" s="4"/>
       <c r="U149" s="4"/>
       <c r="V149" s="4"/>
       <c r="W149" s="4"/>
       <c r="X149" s="4"/>
-      <c r="Y149" s="4"/>
-    </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" s="3"/>
       <c r="B150" s="4"/>
       <c r="C150" s="5"/>
@@ -5221,17 +5047,16 @@
       <c r="N150" s="5"/>
       <c r="O150" s="5"/>
       <c r="P150" s="5"/>
-      <c r="Q150" s="5"/>
-      <c r="R150" s="4"/>
-      <c r="S150" s="6"/>
+      <c r="Q150" s="4"/>
+      <c r="R150" s="6"/>
+      <c r="S150" s="4"/>
       <c r="T150" s="4"/>
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
-      <c r="Y150" s="4"/>
-    </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" s="3"/>
       <c r="B151" s="4"/>
       <c r="C151" s="5"/>
@@ -5248,17 +5073,16 @@
       <c r="N151" s="5"/>
       <c r="O151" s="5"/>
       <c r="P151" s="5"/>
-      <c r="Q151" s="5"/>
-      <c r="R151" s="4"/>
-      <c r="S151" s="6"/>
+      <c r="Q151" s="4"/>
+      <c r="R151" s="6"/>
+      <c r="S151" s="4"/>
       <c r="T151" s="4"/>
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
       <c r="W151" s="4"/>
       <c r="X151" s="4"/>
-      <c r="Y151" s="4"/>
-    </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" s="3"/>
       <c r="B152" s="4"/>
       <c r="C152" s="5"/>
@@ -5275,17 +5099,16 @@
       <c r="N152" s="5"/>
       <c r="O152" s="5"/>
       <c r="P152" s="5"/>
-      <c r="Q152" s="5"/>
-      <c r="R152" s="4"/>
-      <c r="S152" s="6"/>
+      <c r="Q152" s="4"/>
+      <c r="R152" s="6"/>
+      <c r="S152" s="4"/>
       <c r="T152" s="4"/>
       <c r="U152" s="4"/>
       <c r="V152" s="4"/>
       <c r="W152" s="4"/>
       <c r="X152" s="4"/>
-      <c r="Y152" s="4"/>
-    </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" s="3"/>
       <c r="B153" s="4"/>
       <c r="C153" s="5"/>
@@ -5302,17 +5125,16 @@
       <c r="N153" s="5"/>
       <c r="O153" s="5"/>
       <c r="P153" s="5"/>
-      <c r="Q153" s="5"/>
-      <c r="R153" s="4"/>
-      <c r="S153" s="6"/>
+      <c r="Q153" s="4"/>
+      <c r="R153" s="6"/>
+      <c r="S153" s="4"/>
       <c r="T153" s="4"/>
       <c r="U153" s="4"/>
       <c r="V153" s="4"/>
       <c r="W153" s="4"/>
       <c r="X153" s="4"/>
-      <c r="Y153" s="4"/>
-    </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" s="3"/>
       <c r="B154" s="4"/>
       <c r="C154" s="5"/>
@@ -5329,17 +5151,16 @@
       <c r="N154" s="5"/>
       <c r="O154" s="5"/>
       <c r="P154" s="5"/>
-      <c r="Q154" s="5"/>
-      <c r="R154" s="4"/>
-      <c r="S154" s="6"/>
+      <c r="Q154" s="4"/>
+      <c r="R154" s="6"/>
+      <c r="S154" s="4"/>
       <c r="T154" s="4"/>
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
       <c r="W154" s="4"/>
       <c r="X154" s="4"/>
-      <c r="Y154" s="4"/>
-    </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" s="3"/>
       <c r="B155" s="4"/>
       <c r="C155" s="5"/>
@@ -5356,17 +5177,16 @@
       <c r="N155" s="5"/>
       <c r="O155" s="5"/>
       <c r="P155" s="5"/>
-      <c r="Q155" s="5"/>
-      <c r="R155" s="4"/>
-      <c r="S155" s="6"/>
+      <c r="Q155" s="4"/>
+      <c r="R155" s="6"/>
+      <c r="S155" s="4"/>
       <c r="T155" s="4"/>
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
       <c r="W155" s="4"/>
       <c r="X155" s="4"/>
-      <c r="Y155" s="4"/>
-    </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" s="3"/>
       <c r="B156" s="4"/>
       <c r="C156" s="5"/>
@@ -5383,17 +5203,16 @@
       <c r="N156" s="5"/>
       <c r="O156" s="5"/>
       <c r="P156" s="5"/>
-      <c r="Q156" s="5"/>
-      <c r="R156" s="4"/>
-      <c r="S156" s="6"/>
+      <c r="Q156" s="4"/>
+      <c r="R156" s="6"/>
+      <c r="S156" s="4"/>
       <c r="T156" s="4"/>
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
       <c r="W156" s="4"/>
       <c r="X156" s="4"/>
-      <c r="Y156" s="4"/>
-    </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" s="3"/>
       <c r="B157" s="4"/>
       <c r="C157" s="5"/>
@@ -5410,17 +5229,16 @@
       <c r="N157" s="5"/>
       <c r="O157" s="5"/>
       <c r="P157" s="5"/>
-      <c r="Q157" s="5"/>
-      <c r="R157" s="4"/>
-      <c r="S157" s="6"/>
+      <c r="Q157" s="4"/>
+      <c r="R157" s="6"/>
+      <c r="S157" s="4"/>
       <c r="T157" s="4"/>
       <c r="U157" s="4"/>
       <c r="V157" s="4"/>
       <c r="W157" s="4"/>
       <c r="X157" s="4"/>
-      <c r="Y157" s="4"/>
-    </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" s="3"/>
       <c r="B158" s="4"/>
       <c r="C158" s="5"/>
@@ -5437,17 +5255,16 @@
       <c r="N158" s="5"/>
       <c r="O158" s="5"/>
       <c r="P158" s="5"/>
-      <c r="Q158" s="5"/>
-      <c r="R158" s="4"/>
-      <c r="S158" s="6"/>
+      <c r="Q158" s="4"/>
+      <c r="R158" s="6"/>
+      <c r="S158" s="4"/>
       <c r="T158" s="4"/>
       <c r="U158" s="4"/>
       <c r="V158" s="4"/>
       <c r="W158" s="4"/>
       <c r="X158" s="4"/>
-      <c r="Y158" s="4"/>
-    </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" s="3"/>
       <c r="B159" s="4"/>
       <c r="C159" s="5"/>
@@ -5464,17 +5281,16 @@
       <c r="N159" s="5"/>
       <c r="O159" s="5"/>
       <c r="P159" s="5"/>
-      <c r="Q159" s="5"/>
-      <c r="R159" s="4"/>
-      <c r="S159" s="6"/>
+      <c r="Q159" s="4"/>
+      <c r="R159" s="6"/>
+      <c r="S159" s="4"/>
       <c r="T159" s="4"/>
       <c r="U159" s="4"/>
       <c r="V159" s="4"/>
       <c r="W159" s="4"/>
       <c r="X159" s="4"/>
-      <c r="Y159" s="4"/>
-    </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" s="3"/>
       <c r="B160" s="4"/>
       <c r="C160" s="5"/>
@@ -5491,17 +5307,16 @@
       <c r="N160" s="5"/>
       <c r="O160" s="5"/>
       <c r="P160" s="5"/>
-      <c r="Q160" s="5"/>
-      <c r="R160" s="4"/>
-      <c r="S160" s="6"/>
+      <c r="Q160" s="4"/>
+      <c r="R160" s="6"/>
+      <c r="S160" s="4"/>
       <c r="T160" s="4"/>
       <c r="U160" s="4"/>
       <c r="V160" s="4"/>
       <c r="W160" s="4"/>
       <c r="X160" s="4"/>
-      <c r="Y160" s="4"/>
-    </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" s="3"/>
       <c r="B161" s="4"/>
       <c r="C161" s="5"/>
@@ -5518,17 +5333,16 @@
       <c r="N161" s="5"/>
       <c r="O161" s="5"/>
       <c r="P161" s="5"/>
-      <c r="Q161" s="5"/>
-      <c r="R161" s="4"/>
-      <c r="S161" s="6"/>
+      <c r="Q161" s="4"/>
+      <c r="R161" s="6"/>
+      <c r="S161" s="4"/>
       <c r="T161" s="4"/>
       <c r="U161" s="4"/>
       <c r="V161" s="4"/>
       <c r="W161" s="4"/>
       <c r="X161" s="4"/>
-      <c r="Y161" s="4"/>
-    </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" s="3"/>
       <c r="B162" s="4"/>
       <c r="C162" s="5"/>
@@ -5545,17 +5359,16 @@
       <c r="N162" s="5"/>
       <c r="O162" s="5"/>
       <c r="P162" s="5"/>
-      <c r="Q162" s="5"/>
-      <c r="R162" s="4"/>
-      <c r="S162" s="6"/>
+      <c r="Q162" s="4"/>
+      <c r="R162" s="6"/>
+      <c r="S162" s="4"/>
       <c r="T162" s="4"/>
       <c r="U162" s="4"/>
       <c r="V162" s="4"/>
       <c r="W162" s="4"/>
       <c r="X162" s="4"/>
-      <c r="Y162" s="4"/>
-    </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" s="3"/>
       <c r="B163" s="4"/>
       <c r="C163" s="5"/>
@@ -5572,17 +5385,16 @@
       <c r="N163" s="5"/>
       <c r="O163" s="5"/>
       <c r="P163" s="5"/>
-      <c r="Q163" s="5"/>
-      <c r="R163" s="4"/>
-      <c r="S163" s="6"/>
+      <c r="Q163" s="4"/>
+      <c r="R163" s="6"/>
+      <c r="S163" s="4"/>
       <c r="T163" s="4"/>
       <c r="U163" s="4"/>
       <c r="V163" s="4"/>
       <c r="W163" s="4"/>
       <c r="X163" s="4"/>
-      <c r="Y163" s="4"/>
-    </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" s="3"/>
       <c r="B164" s="4"/>
       <c r="C164" s="5"/>
@@ -5599,17 +5411,16 @@
       <c r="N164" s="5"/>
       <c r="O164" s="5"/>
       <c r="P164" s="5"/>
-      <c r="Q164" s="5"/>
-      <c r="R164" s="4"/>
-      <c r="S164" s="6"/>
+      <c r="Q164" s="4"/>
+      <c r="R164" s="6"/>
+      <c r="S164" s="4"/>
       <c r="T164" s="4"/>
       <c r="U164" s="4"/>
       <c r="V164" s="4"/>
       <c r="W164" s="4"/>
       <c r="X164" s="4"/>
-      <c r="Y164" s="4"/>
-    </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" s="3"/>
       <c r="B165" s="4"/>
       <c r="C165" s="5"/>
@@ -5626,17 +5437,16 @@
       <c r="N165" s="5"/>
       <c r="O165" s="5"/>
       <c r="P165" s="5"/>
-      <c r="Q165" s="5"/>
-      <c r="R165" s="4"/>
-      <c r="S165" s="6"/>
+      <c r="Q165" s="4"/>
+      <c r="R165" s="6"/>
+      <c r="S165" s="4"/>
       <c r="T165" s="4"/>
       <c r="U165" s="4"/>
       <c r="V165" s="4"/>
       <c r="W165" s="4"/>
       <c r="X165" s="4"/>
-      <c r="Y165" s="4"/>
-    </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" s="3"/>
       <c r="B166" s="4"/>
       <c r="C166" s="5"/>
@@ -5653,17 +5463,16 @@
       <c r="N166" s="5"/>
       <c r="O166" s="5"/>
       <c r="P166" s="5"/>
-      <c r="Q166" s="5"/>
-      <c r="R166" s="4"/>
-      <c r="S166" s="6"/>
+      <c r="Q166" s="4"/>
+      <c r="R166" s="6"/>
+      <c r="S166" s="4"/>
       <c r="T166" s="4"/>
       <c r="U166" s="4"/>
       <c r="V166" s="4"/>
       <c r="W166" s="4"/>
       <c r="X166" s="4"/>
-      <c r="Y166" s="4"/>
-    </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" s="3"/>
       <c r="B167" s="4"/>
       <c r="C167" s="5"/>
@@ -5680,17 +5489,16 @@
       <c r="N167" s="5"/>
       <c r="O167" s="5"/>
       <c r="P167" s="5"/>
-      <c r="Q167" s="5"/>
-      <c r="R167" s="4"/>
-      <c r="S167" s="6"/>
+      <c r="Q167" s="4"/>
+      <c r="R167" s="6"/>
+      <c r="S167" s="4"/>
       <c r="T167" s="4"/>
       <c r="U167" s="4"/>
       <c r="V167" s="4"/>
       <c r="W167" s="4"/>
       <c r="X167" s="4"/>
-      <c r="Y167" s="4"/>
-    </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" s="3"/>
       <c r="B168" s="4"/>
       <c r="C168" s="5"/>
@@ -5707,17 +5515,16 @@
       <c r="N168" s="5"/>
       <c r="O168" s="5"/>
       <c r="P168" s="5"/>
-      <c r="Q168" s="5"/>
-      <c r="R168" s="4"/>
-      <c r="S168" s="6"/>
+      <c r="Q168" s="4"/>
+      <c r="R168" s="6"/>
+      <c r="S168" s="4"/>
       <c r="T168" s="4"/>
       <c r="U168" s="4"/>
       <c r="V168" s="4"/>
       <c r="W168" s="4"/>
       <c r="X168" s="4"/>
-      <c r="Y168" s="4"/>
-    </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" s="3"/>
       <c r="B169" s="4"/>
       <c r="C169" s="5"/>
@@ -5734,17 +5541,16 @@
       <c r="N169" s="5"/>
       <c r="O169" s="5"/>
       <c r="P169" s="5"/>
-      <c r="Q169" s="5"/>
-      <c r="R169" s="4"/>
-      <c r="S169" s="6"/>
+      <c r="Q169" s="4"/>
+      <c r="R169" s="6"/>
+      <c r="S169" s="4"/>
       <c r="T169" s="4"/>
       <c r="U169" s="4"/>
       <c r="V169" s="4"/>
       <c r="W169" s="4"/>
       <c r="X169" s="4"/>
-      <c r="Y169" s="4"/>
-    </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170" s="3"/>
       <c r="B170" s="4"/>
       <c r="C170" s="5"/>
@@ -5761,17 +5567,16 @@
       <c r="N170" s="5"/>
       <c r="O170" s="5"/>
       <c r="P170" s="5"/>
-      <c r="Q170" s="5"/>
-      <c r="R170" s="4"/>
-      <c r="S170" s="6"/>
+      <c r="Q170" s="4"/>
+      <c r="R170" s="6"/>
+      <c r="S170" s="4"/>
       <c r="T170" s="4"/>
       <c r="U170" s="4"/>
       <c r="V170" s="4"/>
       <c r="W170" s="4"/>
       <c r="X170" s="4"/>
-      <c r="Y170" s="4"/>
-    </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171" s="3"/>
       <c r="B171" s="4"/>
       <c r="C171" s="5"/>
@@ -5788,17 +5593,16 @@
       <c r="N171" s="5"/>
       <c r="O171" s="5"/>
       <c r="P171" s="5"/>
-      <c r="Q171" s="5"/>
-      <c r="R171" s="4"/>
-      <c r="S171" s="6"/>
+      <c r="Q171" s="4"/>
+      <c r="R171" s="6"/>
+      <c r="S171" s="4"/>
       <c r="T171" s="4"/>
       <c r="U171" s="4"/>
       <c r="V171" s="4"/>
       <c r="W171" s="4"/>
       <c r="X171" s="4"/>
-      <c r="Y171" s="4"/>
-    </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172" s="3"/>
       <c r="B172" s="4"/>
       <c r="C172" s="5"/>
@@ -5815,17 +5619,16 @@
       <c r="N172" s="5"/>
       <c r="O172" s="5"/>
       <c r="P172" s="5"/>
-      <c r="Q172" s="5"/>
-      <c r="R172" s="4"/>
-      <c r="S172" s="6"/>
+      <c r="Q172" s="4"/>
+      <c r="R172" s="6"/>
+      <c r="S172" s="4"/>
       <c r="T172" s="4"/>
       <c r="U172" s="4"/>
       <c r="V172" s="4"/>
       <c r="W172" s="4"/>
       <c r="X172" s="4"/>
-      <c r="Y172" s="4"/>
-    </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173" s="3"/>
       <c r="B173" s="4"/>
       <c r="C173" s="5"/>
@@ -5842,17 +5645,16 @@
       <c r="N173" s="5"/>
       <c r="O173" s="5"/>
       <c r="P173" s="5"/>
-      <c r="Q173" s="5"/>
-      <c r="R173" s="4"/>
-      <c r="S173" s="6"/>
+      <c r="Q173" s="4"/>
+      <c r="R173" s="6"/>
+      <c r="S173" s="4"/>
       <c r="T173" s="4"/>
       <c r="U173" s="4"/>
       <c r="V173" s="4"/>
       <c r="W173" s="4"/>
       <c r="X173" s="4"/>
-      <c r="Y173" s="4"/>
-    </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174" s="3"/>
       <c r="B174" s="4"/>
       <c r="C174" s="5"/>
@@ -5869,17 +5671,16 @@
       <c r="N174" s="5"/>
       <c r="O174" s="5"/>
       <c r="P174" s="5"/>
-      <c r="Q174" s="5"/>
-      <c r="R174" s="4"/>
-      <c r="S174" s="6"/>
+      <c r="Q174" s="4"/>
+      <c r="R174" s="6"/>
+      <c r="S174" s="4"/>
       <c r="T174" s="4"/>
       <c r="U174" s="4"/>
       <c r="V174" s="4"/>
       <c r="W174" s="4"/>
       <c r="X174" s="4"/>
-      <c r="Y174" s="4"/>
-    </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175" s="3"/>
       <c r="B175" s="4"/>
       <c r="C175" s="5"/>
@@ -5896,17 +5697,16 @@
       <c r="N175" s="5"/>
       <c r="O175" s="5"/>
       <c r="P175" s="5"/>
-      <c r="Q175" s="5"/>
-      <c r="R175" s="4"/>
-      <c r="S175" s="6"/>
+      <c r="Q175" s="4"/>
+      <c r="R175" s="6"/>
+      <c r="S175" s="4"/>
       <c r="T175" s="4"/>
       <c r="U175" s="4"/>
       <c r="V175" s="4"/>
       <c r="W175" s="4"/>
       <c r="X175" s="4"/>
-      <c r="Y175" s="4"/>
-    </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176" s="3"/>
       <c r="B176" s="4"/>
       <c r="C176" s="5"/>
@@ -5923,17 +5723,16 @@
       <c r="N176" s="5"/>
       <c r="O176" s="5"/>
       <c r="P176" s="5"/>
-      <c r="Q176" s="5"/>
-      <c r="R176" s="4"/>
-      <c r="S176" s="6"/>
+      <c r="Q176" s="4"/>
+      <c r="R176" s="6"/>
+      <c r="S176" s="4"/>
       <c r="T176" s="4"/>
       <c r="U176" s="4"/>
       <c r="V176" s="4"/>
       <c r="W176" s="4"/>
       <c r="X176" s="4"/>
-      <c r="Y176" s="4"/>
-    </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" s="3"/>
       <c r="B177" s="4"/>
       <c r="C177" s="5"/>
@@ -5950,17 +5749,16 @@
       <c r="N177" s="5"/>
       <c r="O177" s="5"/>
       <c r="P177" s="5"/>
-      <c r="Q177" s="5"/>
-      <c r="R177" s="4"/>
-      <c r="S177" s="6"/>
+      <c r="Q177" s="4"/>
+      <c r="R177" s="6"/>
+      <c r="S177" s="4"/>
       <c r="T177" s="4"/>
       <c r="U177" s="4"/>
       <c r="V177" s="4"/>
       <c r="W177" s="4"/>
       <c r="X177" s="4"/>
-      <c r="Y177" s="4"/>
-    </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A178" s="3"/>
       <c r="B178" s="4"/>
       <c r="C178" s="5"/>
@@ -5977,17 +5775,16 @@
       <c r="N178" s="5"/>
       <c r="O178" s="5"/>
       <c r="P178" s="5"/>
-      <c r="Q178" s="5"/>
-      <c r="R178" s="4"/>
-      <c r="S178" s="6"/>
+      <c r="Q178" s="4"/>
+      <c r="R178" s="6"/>
+      <c r="S178" s="4"/>
       <c r="T178" s="4"/>
       <c r="U178" s="4"/>
       <c r="V178" s="4"/>
       <c r="W178" s="4"/>
       <c r="X178" s="4"/>
-      <c r="Y178" s="4"/>
-    </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A179" s="3"/>
       <c r="B179" s="4"/>
       <c r="C179" s="5"/>
@@ -6004,17 +5801,16 @@
       <c r="N179" s="5"/>
       <c r="O179" s="5"/>
       <c r="P179" s="5"/>
-      <c r="Q179" s="5"/>
-      <c r="R179" s="4"/>
-      <c r="S179" s="6"/>
+      <c r="Q179" s="4"/>
+      <c r="R179" s="6"/>
+      <c r="S179" s="4"/>
       <c r="T179" s="4"/>
       <c r="U179" s="4"/>
       <c r="V179" s="4"/>
       <c r="W179" s="4"/>
       <c r="X179" s="4"/>
-      <c r="Y179" s="4"/>
-    </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A180" s="3"/>
       <c r="B180" s="4"/>
       <c r="C180" s="5"/>
@@ -6031,17 +5827,16 @@
       <c r="N180" s="5"/>
       <c r="O180" s="5"/>
       <c r="P180" s="5"/>
-      <c r="Q180" s="5"/>
-      <c r="R180" s="4"/>
-      <c r="S180" s="6"/>
+      <c r="Q180" s="4"/>
+      <c r="R180" s="6"/>
+      <c r="S180" s="4"/>
       <c r="T180" s="4"/>
       <c r="U180" s="4"/>
       <c r="V180" s="4"/>
       <c r="W180" s="4"/>
       <c r="X180" s="4"/>
-      <c r="Y180" s="4"/>
-    </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A181" s="3"/>
       <c r="B181" s="4"/>
       <c r="C181" s="5"/>
@@ -6058,17 +5853,16 @@
       <c r="N181" s="5"/>
       <c r="O181" s="5"/>
       <c r="P181" s="5"/>
-      <c r="Q181" s="5"/>
-      <c r="R181" s="4"/>
-      <c r="S181" s="6"/>
+      <c r="Q181" s="4"/>
+      <c r="R181" s="6"/>
+      <c r="S181" s="4"/>
       <c r="T181" s="4"/>
       <c r="U181" s="4"/>
       <c r="V181" s="4"/>
       <c r="W181" s="4"/>
       <c r="X181" s="4"/>
-      <c r="Y181" s="4"/>
-    </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A182" s="3"/>
       <c r="B182" s="4"/>
       <c r="C182" s="5"/>
@@ -6085,17 +5879,16 @@
       <c r="N182" s="5"/>
       <c r="O182" s="5"/>
       <c r="P182" s="5"/>
-      <c r="Q182" s="5"/>
-      <c r="R182" s="4"/>
-      <c r="S182" s="6"/>
+      <c r="Q182" s="4"/>
+      <c r="R182" s="6"/>
+      <c r="S182" s="4"/>
       <c r="T182" s="4"/>
       <c r="U182" s="4"/>
       <c r="V182" s="4"/>
       <c r="W182" s="4"/>
       <c r="X182" s="4"/>
-      <c r="Y182" s="4"/>
-    </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A183" s="3"/>
       <c r="B183" s="4"/>
       <c r="C183" s="5"/>
@@ -6112,17 +5905,16 @@
       <c r="N183" s="5"/>
       <c r="O183" s="5"/>
       <c r="P183" s="5"/>
-      <c r="Q183" s="5"/>
-      <c r="R183" s="4"/>
-      <c r="S183" s="6"/>
+      <c r="Q183" s="4"/>
+      <c r="R183" s="6"/>
+      <c r="S183" s="4"/>
       <c r="T183" s="4"/>
       <c r="U183" s="4"/>
       <c r="V183" s="4"/>
       <c r="W183" s="4"/>
       <c r="X183" s="4"/>
-      <c r="Y183" s="4"/>
-    </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A184" s="3"/>
       <c r="B184" s="4"/>
       <c r="C184" s="5"/>
@@ -6139,17 +5931,16 @@
       <c r="N184" s="5"/>
       <c r="O184" s="5"/>
       <c r="P184" s="5"/>
-      <c r="Q184" s="5"/>
-      <c r="R184" s="4"/>
-      <c r="S184" s="6"/>
+      <c r="Q184" s="4"/>
+      <c r="R184" s="6"/>
+      <c r="S184" s="4"/>
       <c r="T184" s="4"/>
       <c r="U184" s="4"/>
       <c r="V184" s="4"/>
       <c r="W184" s="4"/>
       <c r="X184" s="4"/>
-      <c r="Y184" s="4"/>
-    </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A185" s="3"/>
       <c r="B185" s="4"/>
       <c r="C185" s="5"/>
@@ -6166,17 +5957,16 @@
       <c r="N185" s="5"/>
       <c r="O185" s="5"/>
       <c r="P185" s="5"/>
-      <c r="Q185" s="5"/>
-      <c r="R185" s="4"/>
-      <c r="S185" s="6"/>
+      <c r="Q185" s="4"/>
+      <c r="R185" s="6"/>
+      <c r="S185" s="4"/>
       <c r="T185" s="4"/>
       <c r="U185" s="4"/>
       <c r="V185" s="4"/>
       <c r="W185" s="4"/>
       <c r="X185" s="4"/>
-      <c r="Y185" s="4"/>
-    </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A186" s="3"/>
       <c r="B186" s="4"/>
       <c r="C186" s="5"/>
@@ -6193,17 +5983,16 @@
       <c r="N186" s="5"/>
       <c r="O186" s="5"/>
       <c r="P186" s="5"/>
-      <c r="Q186" s="5"/>
-      <c r="R186" s="4"/>
-      <c r="S186" s="6"/>
+      <c r="Q186" s="4"/>
+      <c r="R186" s="6"/>
+      <c r="S186" s="4"/>
       <c r="T186" s="4"/>
       <c r="U186" s="4"/>
       <c r="V186" s="4"/>
       <c r="W186" s="4"/>
       <c r="X186" s="4"/>
-      <c r="Y186" s="4"/>
-    </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A187" s="3"/>
       <c r="B187" s="4"/>
       <c r="C187" s="5"/>
@@ -6220,17 +6009,16 @@
       <c r="N187" s="5"/>
       <c r="O187" s="5"/>
       <c r="P187" s="5"/>
-      <c r="Q187" s="5"/>
-      <c r="R187" s="4"/>
-      <c r="S187" s="6"/>
+      <c r="Q187" s="4"/>
+      <c r="R187" s="6"/>
+      <c r="S187" s="4"/>
       <c r="T187" s="4"/>
       <c r="U187" s="4"/>
       <c r="V187" s="4"/>
       <c r="W187" s="4"/>
       <c r="X187" s="4"/>
-      <c r="Y187" s="4"/>
-    </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A188" s="3"/>
       <c r="B188" s="4"/>
       <c r="C188" s="5"/>
@@ -6247,17 +6035,16 @@
       <c r="N188" s="5"/>
       <c r="O188" s="5"/>
       <c r="P188" s="5"/>
-      <c r="Q188" s="5"/>
-      <c r="R188" s="4"/>
-      <c r="S188" s="6"/>
+      <c r="Q188" s="4"/>
+      <c r="R188" s="6"/>
+      <c r="S188" s="4"/>
       <c r="T188" s="4"/>
       <c r="U188" s="4"/>
       <c r="V188" s="4"/>
       <c r="W188" s="4"/>
       <c r="X188" s="4"/>
-      <c r="Y188" s="4"/>
-    </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A189" s="3"/>
       <c r="B189" s="4"/>
       <c r="C189" s="5"/>
@@ -6274,17 +6061,16 @@
       <c r="N189" s="5"/>
       <c r="O189" s="5"/>
       <c r="P189" s="5"/>
-      <c r="Q189" s="5"/>
-      <c r="R189" s="4"/>
-      <c r="S189" s="6"/>
+      <c r="Q189" s="4"/>
+      <c r="R189" s="6"/>
+      <c r="S189" s="4"/>
       <c r="T189" s="4"/>
       <c r="U189" s="4"/>
       <c r="V189" s="4"/>
       <c r="W189" s="4"/>
       <c r="X189" s="4"/>
-      <c r="Y189" s="4"/>
-    </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A190" s="3"/>
       <c r="B190" s="4"/>
       <c r="C190" s="5"/>
@@ -6301,17 +6087,16 @@
       <c r="N190" s="5"/>
       <c r="O190" s="5"/>
       <c r="P190" s="5"/>
-      <c r="Q190" s="5"/>
-      <c r="R190" s="4"/>
-      <c r="S190" s="6"/>
+      <c r="Q190" s="4"/>
+      <c r="R190" s="6"/>
+      <c r="S190" s="4"/>
       <c r="T190" s="4"/>
       <c r="U190" s="4"/>
       <c r="V190" s="4"/>
       <c r="W190" s="4"/>
       <c r="X190" s="4"/>
-      <c r="Y190" s="4"/>
-    </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
       <c r="B191" s="4"/>
       <c r="C191" s="5"/>
@@ -6328,17 +6113,16 @@
       <c r="N191" s="5"/>
       <c r="O191" s="5"/>
       <c r="P191" s="5"/>
-      <c r="Q191" s="5"/>
-      <c r="R191" s="4"/>
-      <c r="S191" s="6"/>
+      <c r="Q191" s="4"/>
+      <c r="R191" s="6"/>
+      <c r="S191" s="4"/>
       <c r="T191" s="4"/>
       <c r="U191" s="4"/>
       <c r="V191" s="4"/>
       <c r="W191" s="4"/>
       <c r="X191" s="4"/>
-      <c r="Y191" s="4"/>
-    </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A192" s="3"/>
       <c r="B192" s="4"/>
       <c r="C192" s="5"/>
@@ -6355,17 +6139,16 @@
       <c r="N192" s="5"/>
       <c r="O192" s="5"/>
       <c r="P192" s="5"/>
-      <c r="Q192" s="5"/>
-      <c r="R192" s="4"/>
-      <c r="S192" s="6"/>
+      <c r="Q192" s="4"/>
+      <c r="R192" s="6"/>
+      <c r="S192" s="4"/>
       <c r="T192" s="4"/>
       <c r="U192" s="4"/>
       <c r="V192" s="4"/>
       <c r="W192" s="4"/>
       <c r="X192" s="4"/>
-      <c r="Y192" s="4"/>
-    </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="4"/>
       <c r="C193" s="5"/>
@@ -6382,17 +6165,16 @@
       <c r="N193" s="5"/>
       <c r="O193" s="5"/>
       <c r="P193" s="5"/>
-      <c r="Q193" s="5"/>
-      <c r="R193" s="4"/>
-      <c r="S193" s="6"/>
+      <c r="Q193" s="4"/>
+      <c r="R193" s="6"/>
+      <c r="S193" s="4"/>
       <c r="T193" s="4"/>
       <c r="U193" s="4"/>
       <c r="V193" s="4"/>
       <c r="W193" s="4"/>
       <c r="X193" s="4"/>
-      <c r="Y193" s="4"/>
-    </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A194" s="3"/>
       <c r="B194" s="4"/>
       <c r="C194" s="5"/>
@@ -6409,17 +6191,16 @@
       <c r="N194" s="5"/>
       <c r="O194" s="5"/>
       <c r="P194" s="5"/>
-      <c r="Q194" s="5"/>
-      <c r="R194" s="4"/>
-      <c r="S194" s="6"/>
+      <c r="Q194" s="4"/>
+      <c r="R194" s="6"/>
+      <c r="S194" s="4"/>
       <c r="T194" s="4"/>
       <c r="U194" s="4"/>
       <c r="V194" s="4"/>
       <c r="W194" s="4"/>
       <c r="X194" s="4"/>
-      <c r="Y194" s="4"/>
-    </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A195" s="3"/>
       <c r="B195" s="4"/>
       <c r="C195" s="5"/>
@@ -6436,17 +6217,16 @@
       <c r="N195" s="5"/>
       <c r="O195" s="5"/>
       <c r="P195" s="5"/>
-      <c r="Q195" s="5"/>
-      <c r="R195" s="4"/>
-      <c r="S195" s="6"/>
+      <c r="Q195" s="4"/>
+      <c r="R195" s="6"/>
+      <c r="S195" s="4"/>
       <c r="T195" s="4"/>
       <c r="U195" s="4"/>
       <c r="V195" s="4"/>
       <c r="W195" s="4"/>
       <c r="X195" s="4"/>
-      <c r="Y195" s="4"/>
-    </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A196" s="3"/>
       <c r="B196" s="4"/>
       <c r="C196" s="5"/>
@@ -6463,17 +6243,16 @@
       <c r="N196" s="5"/>
       <c r="O196" s="5"/>
       <c r="P196" s="5"/>
-      <c r="Q196" s="5"/>
-      <c r="R196" s="4"/>
-      <c r="S196" s="6"/>
+      <c r="Q196" s="4"/>
+      <c r="R196" s="6"/>
+      <c r="S196" s="4"/>
       <c r="T196" s="4"/>
       <c r="U196" s="4"/>
       <c r="V196" s="4"/>
       <c r="W196" s="4"/>
       <c r="X196" s="4"/>
-      <c r="Y196" s="4"/>
-    </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A197" s="3"/>
       <c r="B197" s="4"/>
       <c r="C197" s="5"/>
@@ -6490,17 +6269,16 @@
       <c r="N197" s="5"/>
       <c r="O197" s="5"/>
       <c r="P197" s="5"/>
-      <c r="Q197" s="5"/>
-      <c r="R197" s="4"/>
-      <c r="S197" s="6"/>
+      <c r="Q197" s="4"/>
+      <c r="R197" s="6"/>
+      <c r="S197" s="4"/>
       <c r="T197" s="4"/>
       <c r="U197" s="4"/>
       <c r="V197" s="4"/>
       <c r="W197" s="4"/>
       <c r="X197" s="4"/>
-      <c r="Y197" s="4"/>
-    </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A198" s="3"/>
       <c r="B198" s="4"/>
       <c r="C198" s="5"/>
@@ -6517,17 +6295,16 @@
       <c r="N198" s="5"/>
       <c r="O198" s="5"/>
       <c r="P198" s="5"/>
-      <c r="Q198" s="5"/>
-      <c r="R198" s="4"/>
-      <c r="S198" s="6"/>
+      <c r="Q198" s="4"/>
+      <c r="R198" s="6"/>
+      <c r="S198" s="4"/>
       <c r="T198" s="4"/>
       <c r="U198" s="4"/>
       <c r="V198" s="4"/>
       <c r="W198" s="4"/>
       <c r="X198" s="4"/>
-      <c r="Y198" s="4"/>
-    </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
       <c r="B199" s="4"/>
       <c r="C199" s="5"/>
@@ -6544,17 +6321,16 @@
       <c r="N199" s="5"/>
       <c r="O199" s="5"/>
       <c r="P199" s="5"/>
-      <c r="Q199" s="5"/>
-      <c r="R199" s="4"/>
-      <c r="S199" s="6"/>
+      <c r="Q199" s="4"/>
+      <c r="R199" s="6"/>
+      <c r="S199" s="4"/>
       <c r="T199" s="4"/>
       <c r="U199" s="4"/>
       <c r="V199" s="4"/>
       <c r="W199" s="4"/>
       <c r="X199" s="4"/>
-      <c r="Y199" s="4"/>
-    </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A200" s="3"/>
       <c r="B200" s="4"/>
       <c r="C200" s="5"/>
@@ -6571,17 +6347,16 @@
       <c r="N200" s="5"/>
       <c r="O200" s="5"/>
       <c r="P200" s="5"/>
-      <c r="Q200" s="5"/>
-      <c r="R200" s="4"/>
-      <c r="S200" s="6"/>
+      <c r="Q200" s="4"/>
+      <c r="R200" s="6"/>
+      <c r="S200" s="4"/>
       <c r="T200" s="4"/>
       <c r="U200" s="4"/>
       <c r="V200" s="4"/>
       <c r="W200" s="4"/>
       <c r="X200" s="4"/>
-      <c r="Y200" s="4"/>
-    </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A201" s="3"/>
       <c r="B201" s="4"/>
       <c r="C201" s="5"/>
@@ -6598,15 +6373,14 @@
       <c r="N201" s="5"/>
       <c r="O201" s="5"/>
       <c r="P201" s="5"/>
-      <c r="Q201" s="5"/>
-      <c r="R201" s="4"/>
-      <c r="S201" s="6"/>
+      <c r="Q201" s="4"/>
+      <c r="R201" s="6"/>
+      <c r="S201" s="4"/>
       <c r="T201" s="4"/>
       <c r="U201" s="4"/>
       <c r="V201" s="4"/>
       <c r="W201" s="4"/>
       <c r="X201" s="4"/>
-      <c r="Y201" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -6625,7 +6399,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -6634,42 +6408,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -6677,55 +6451,55 @@
         <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -6733,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -6741,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -6749,7 +6523,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -6757,7 +6531,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -6765,7 +6539,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6773,7 +6547,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -6781,7 +6555,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -6789,7 +6563,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -6797,7 +6571,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -6805,7 +6579,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -6813,7 +6587,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -6821,7 +6595,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -6829,7 +6603,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -6837,7 +6611,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -6845,7 +6619,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -6853,31 +6627,31 @@
         <v>15</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="8" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -6885,7 +6659,7 @@
         <v>19</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -6893,7 +6667,7 @@
         <v>20</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -6901,7 +6675,7 @@
         <v>21</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -6909,7 +6683,7 @@
         <v>22</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -6917,15 +6691,7 @@
         <v>23</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
